--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_343_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_343_R35.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6909</v>
+        <v>5.9268</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2658</v>
+        <v>4.5017</v>
       </c>
       <c r="F2" t="n">
         <v>1.425</v>
@@ -610,10 +610,10 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6449</v>
+        <v>-0.409</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2082</v>
+        <v>0.0277</v>
       </c>
       <c r="U2" t="n">
         <v>-0.4367</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5713</v>
+        <v>3.6728</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8497</v>
+        <v>3.0856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7217</v>
+        <v>0.5873</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0626</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.6409</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4323</v>
+        <v>-0.1964</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3101</v>
+        <v>-0.4446</v>
       </c>
       <c r="V3" t="n">
         <v>3.2166</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3434</v>
+        <v>2.2311</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9758</v>
+        <v>1.7962</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3676</v>
+        <v>0.4349</v>
       </c>
       <c r="G4" t="n">
         <v>2.2135</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>0.666</v>
+        <v>-0.4463</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1641</v>
+        <v>-0.0154</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4982</v>
+        <v>-0.4309</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2768</v>
+        <v>0.8386</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0876</v>
+        <v>2.6158</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8108</v>
+        <v>-1.7772</v>
       </c>
       <c r="G5" t="n">
         <v>1.3291</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4116</v>
+        <v>-0.0266</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8022</v>
+        <v>0.3304</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3905</v>
+        <v>-0.3569</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4292</v>
+        <v>0.1434</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7085</v>
+        <v>3.1803</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1378</v>
+        <v>-3.0369</v>
       </c>
       <c r="G6" t="n">
         <v>3.3878</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2656</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9709</v>
+        <v>-0.4991</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2948</v>
+        <v>-0.1939</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.17</v>
+        <v>-0.7819</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7832</v>
+        <v>-0.1935</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3868</v>
+        <v>-0.5884</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9857</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7204</v>
+        <v>-0.3323</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8136</v>
+        <v>-0.2238</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0931</v>
+        <v>-0.1085</v>
       </c>
       <c r="V7" t="n">
         <v>1.0722</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. EDWARDS</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3128</v>
+        <v>-1.1659</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0615</v>
+        <v>0.2532</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3743</v>
+        <v>-1.4191</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2933</v>
+        <v>-0.1542</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3301</v>
+        <v>0.4211</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0368</v>
+        <v>-0.5753</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0536</v>
+        <v>1.1828</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0168</v>
+        <v>1.7484</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0368</v>
+        <v>-0.5655</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3469</v>
+        <v>-1.3371</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3469</v>
+        <v>-1.3273</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.0098</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0527</v>
+        <v>-1.388</v>
       </c>
       <c r="T8" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.7544999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0448</v>
+        <v>-0.6335</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X8" t="n">
         <v>-1.0722</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. RANDOLPH</t>
+          <t>K. EDWARDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3314</v>
+        <v>-1.2455</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3982</v>
+        <v>0.0615</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9332</v>
+        <v>-1.3071</v>
       </c>
       <c r="G9" t="n">
-        <v>0.028</v>
+        <v>-0.2933</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4261</v>
+        <v>-0.3301</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3982</v>
+        <v>0.0368</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0603</v>
+        <v>0.0536</v>
       </c>
       <c r="K9" t="n">
-        <v>0.773</v>
+        <v>0.0168</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7127</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0323</v>
+        <v>-0.3469</v>
       </c>
       <c r="N9" t="n">
         <v>-0.3469</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3145</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3365</v>
+        <v>0.1199</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1652</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1713</v>
+        <v>0.112</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>L. RANDOLPH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4359</v>
+        <v>-1.2807</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1326</v>
+        <v>-0.2802</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3033</v>
+        <v>-1.0004</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3409</v>
+        <v>0.028</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6554</v>
+        <v>0.4261</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3145</v>
+        <v>-0.3982</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0168</v>
+        <v>0.0603</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0168</v>
+        <v>0.773</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.7127</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3577</v>
+        <v>-0.0323</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6722</v>
+        <v>-0.3469</v>
       </c>
       <c r="O10" t="n">
         <v>0.3145</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0228</v>
+        <v>0.3872</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1494</v>
+        <v>0.2831</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1265</v>
+        <v>0.1041</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X10" t="n">
         <v>-1.0722</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6822</v>
+        <v>-1.5703</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8753</v>
+        <v>-0.1326</v>
       </c>
       <c r="F11" t="n">
-        <v>2.193</v>
+        <v>-1.4378</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1998</v>
+        <v>-0.3409</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8825</v>
+        <v>-0.6554</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6827</v>
+        <v>0.3145</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1576</v>
+        <v>0.0168</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.268</v>
+        <v>0.0168</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1104</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9579</v>
+        <v>-0.3577</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3856</v>
+        <v>-0.6722</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5723</v>
+        <v>0.3145</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4042</v>
+        <v>-0.1573</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6018</v>
+        <v>-0.1494</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1977</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5051</v>
+        <v>-1.0722</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5051</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.89</v>
+        <v>-2.1376</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3365</v>
+        <v>-4.465</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5535</v>
+        <v>2.3275</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1542</v>
+        <v>-1.1998</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4211</v>
+        <v>-1.8825</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5753</v>
+        <v>0.6827</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1828</v>
+        <v>-2.1576</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7484</v>
+        <v>-2.268</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5655</v>
+        <v>0.1104</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3371</v>
+        <v>0.9579</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3273</v>
+        <v>0.3856</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0098</v>
+        <v>0.5723</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.1121</v>
+        <v>-0.0512</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3443</v>
+        <v>0.0121</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7679</v>
+        <v>-0.0633</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0722</v>
+        <v>0.5051</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0722</v>
+        <v>0.5051</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.630900000000001</v>
+        <v>4.6308</v>
       </c>
       <c r="E13" t="n">
-        <v>10.4231</v>
+        <v>10.423</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.792400000000001</v>
+        <v>-5.792199999999999</v>
       </c>
       <c r="G13" t="n">
         <v>6.023099999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7864</v>
+        <v>-0.7864000000000002</v>
       </c>
       <c r="I13" t="n">
-        <v>6.809399999999998</v>
+        <v>6.809399999999999</v>
       </c>
       <c r="J13" t="n">
         <v>12.8702</v>
@@ -1453,7 +1453,7 @@
         <v>-6.847099999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.370699999999999</v>
+        <v>-8.370700000000001</v>
       </c>
       <c r="O13" t="n">
         <v>1.5235</v>
@@ -1468,16 +1468,16 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6372</v>
+        <v>-3.637500000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1775</v>
+        <v>-1.1774</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.4602</v>
+        <v>-2.4601</v>
       </c>
       <c r="V13" t="n">
-        <v>5.724299999999999</v>
+        <v>5.7243</v>
       </c>
       <c r="W13" t="n">
         <v>10.3277</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4568</v>
+        <v>5.9457</v>
       </c>
       <c r="E14" t="n">
-        <v>8.007899999999999</v>
+        <v>6.2386</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.551</v>
+        <v>-0.2929</v>
       </c>
       <c r="G14" t="n">
         <v>2.2903</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>3.311</v>
+        <v>1.7998</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9688</v>
+        <v>1.1995</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3422</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4652</v>
+        <v>2.0467</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0871</v>
+        <v>5.0847</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.622</v>
+        <v>-3.038</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7917</v>
+        <v>2.7233</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0359</v>
+        <v>1.7899</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2442</v>
+        <v>0.9334</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0062</v>
+        <v>4.8219</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9326</v>
+        <v>3.0956</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0736</v>
+        <v>1.7263</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2144</v>
+        <v>-2.0986</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1034</v>
+        <v>-1.3057</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3178</v>
+        <v>-0.7929</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0187</v>
+        <v>0.8415</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0499</v>
+        <v>0.3503</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0312</v>
+        <v>0.4911</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0412</v>
+        <v>-1.7501</v>
       </c>
       <c r="W15" t="n">
-        <v>0.031</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-2.8223</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4324</v>
+        <v>1.8976</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9212</v>
+        <v>2.2615</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5112</v>
+        <v>-0.3639</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9813</v>
+        <v>1.7917</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8174</v>
+        <v>2.0359</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1639</v>
+        <v>-0.2442</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4568</v>
+        <v>2.0062</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0286</v>
+        <v>1.9326</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4282</v>
+        <v>0.0736</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4755</v>
+        <v>-0.2144</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2112</v>
+        <v>0.1034</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2643</v>
+        <v>-0.3178</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3892</v>
+        <v>0.4512</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4481</v>
+        <v>0.2243</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0589</v>
+        <v>0.2269</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>-1.0412</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.031</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.521</v>
+        <v>1.5503</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2072</v>
+        <v>1.0391</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7282</v>
+        <v>0.5112</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1098</v>
+        <v>0.9813</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1633</v>
+        <v>0.8174</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0535</v>
+        <v>0.1639</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0168</v>
+        <v>1.4568</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0168</v>
+        <v>1.0286</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.4282</v>
       </c>
       <c r="M17" t="n">
-        <v>0.093</v>
+        <v>-0.4755</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1465</v>
+        <v>-0.2112</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0535</v>
+        <v>-0.2643</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0527</v>
+        <v>-0.2713</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.224</v>
+        <v>-0.3301</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1713</v>
+        <v>0.0589</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4347</v>
+        <v>0.611</v>
       </c>
       <c r="E18" t="n">
-        <v>3.7872</v>
+        <v>-0.2072</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.3526</v>
+        <v>0.8183</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7233</v>
+        <v>0.1098</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7899</v>
+        <v>0.1633</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9334</v>
+        <v>-0.0535</v>
       </c>
       <c r="J18" t="n">
-        <v>4.8219</v>
+        <v>0.0168</v>
       </c>
       <c r="K18" t="n">
-        <v>3.0956</v>
+        <v>0.0168</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7263</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0986</v>
+        <v>0.093</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3057</v>
+        <v>0.1465</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7929</v>
+        <v>-0.0535</v>
       </c>
       <c r="P18" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7705</v>
+        <v>0.0373</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.224</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1766</v>
+        <v>0.2614</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.8223</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0092</v>
+        <v>-0.2219</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7453</v>
+        <v>0.1279</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7361</v>
+        <v>-0.3498</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.388</v>
+        <v>-0.7704</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1909</v>
+        <v>-0.767</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5788</v>
+        <v>-0.0034</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0336</v>
+        <v>-0.0766</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0336</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.1607</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4216</v>
+        <v>-0.6938</v>
       </c>
       <c r="N19" t="n">
+        <v>-0.851</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.1573</v>
       </c>
-      <c r="O19" t="n">
-        <v>-0.5788</v>
-      </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3971</v>
+        <v>0.3165</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7117</v>
+        <v>0.2045</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3145</v>
+        <v>0.112</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.643</v>
+        <v>-0.3054</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.226</v>
+        <v>0.2735</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.417</v>
+        <v>-0.5788</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7704</v>
+        <v>-0.388</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.767</v>
+        <v>0.1909</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0034</v>
+        <v>-0.5788</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0766</v>
+        <v>0.0336</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0336</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6938</v>
+        <v>-0.4216</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.851</v>
+        <v>0.1573</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1573</v>
+        <v>-0.5788</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1046</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>0.2399</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0448</v>
+        <v>-0.1573</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5415</v>
+        <v>-0.9752</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6486</v>
+        <v>-1.3511</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1071</v>
+        <v>0.376</v>
       </c>
       <c r="G21" t="n">
         <v>-4.7444</v>
@@ -2092,13 +2092,13 @@
         <v>2.0876</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9568</v>
+        <v>0.6095</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0965</v>
+        <v>0.201</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1397</v>
+        <v>0.4086</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8409</v>
+        <v>-3.5923</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1819</v>
+        <v>-3.6537</v>
       </c>
       <c r="F22" t="n">
-        <v>0.341</v>
+        <v>0.0614</v>
       </c>
       <c r="G22" t="n">
         <v>-5.4956</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>1.9615</v>
+        <v>1.21</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1132</v>
+        <v>0.6414</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.5687</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9304</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3197</v>
+        <v>-3.8188</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8529</v>
+        <v>-2.2067</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4668</v>
+        <v>-1.612</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3963</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7183</v>
+        <v>0.2192</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4288</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2895</v>
+        <v>0.1443</v>
       </c>
       <c r="V23" t="n">
         <v>0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.605</v>
+        <v>-6.1959</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6399</v>
+        <v>-1.8142</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.9651</v>
+        <v>-4.3817</v>
       </c>
       <c r="G24" t="n">
         <v>-1.1249</v>
@@ -2326,13 +2326,13 @@
         <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4954</v>
+        <v>-0.0863</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.1215</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5482</v>
+        <v>0.0351</v>
       </c>
       <c r="V24" t="n">
         <v>-4.2888</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.630799999999998</v>
+        <v>-3.0582</v>
       </c>
       <c r="E25" t="n">
-        <v>5.792199999999998</v>
+        <v>5.792399999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.4231</v>
+        <v>-8.850200000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-6.023199999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7864000000000007</v>
+        <v>0.7863999999999998</v>
       </c>
       <c r="I25" t="n">
         <v>-6.8095</v>
@@ -2380,7 +2380,7 @@
         <v>6.847100000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>8.370899999999999</v>
+        <v>8.370900000000001</v>
       </c>
       <c r="L25" t="n">
         <v>-1.5239</v>
@@ -2404,19 +2404,19 @@
         <v>11.5978</v>
       </c>
       <c r="S25" t="n">
-        <v>3.6374</v>
+        <v>5.21</v>
       </c>
       <c r="T25" t="n">
-        <v>2.460199999999999</v>
+        <v>2.4602</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1774</v>
+        <v>2.75</v>
       </c>
       <c r="V25" t="n">
         <v>-5.724299999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>4.603400000000001</v>
+        <v>4.6034</v>
       </c>
       <c r="X25" t="n">
         <v>-10.3277</v>
